--- a/data/raw/commercial_banking_monthly.xlsx
+++ b/data/raw/commercial_banking_monthly.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Detail" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Monthly Detail'!$A$1:$E$481</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Monthly Detail'!$A$1:$E$493</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,40 +445,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E481"/>
+  <dimension ref="A1:E493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t xml:space="preserve">Reporting Date </t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Measure Name</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Scenario</t>
+          <t>Plan Type</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Value_MM</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Currency Unit</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t xml:space="preserve"> budget </t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -640,7 +640,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Treasury Fee</t>
+          <t xml:space="preserve">Treasury Fee </t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -748,9 +748,7 @@
           <t>Forecast</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>0.9340000000000001</v>
-      </c>
+      <c r="D12" s="3" t="inlineStr"/>
       <c r="E12" s="3" t="inlineStr">
         <is>
           <t>USD millions</t>
@@ -1623,9 +1621,6 @@
           <t>Budget</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>1.193</v>
-      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>USD millions</t>
@@ -2245,7 +2240,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Forecast</t>
+          <t xml:space="preserve"> forecast </t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
@@ -2448,9 +2443,7 @@
           <t>Forecast</t>
         </is>
       </c>
-      <c r="D80" s="3" t="n">
-        <v>1.225</v>
-      </c>
+      <c r="D80" s="3" t="inlineStr"/>
       <c r="E80" s="3" t="inlineStr">
         <is>
           <t>USD millions</t>
@@ -2999,7 +2992,7 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>2.436</v>
+        <v>48.72</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
@@ -3273,9 +3266,6 @@
           <t>Prior Year</t>
         </is>
       </c>
-      <c r="D113" t="n">
-        <v>1.15</v>
-      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>USD millions</t>
@@ -3874,7 +3864,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>2.261</v>
+        <v>45.22</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -3970,7 +3960,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Prior Year</t>
+          <t xml:space="preserve"> prior year </t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -4148,9 +4138,7 @@
           <t>Forecast</t>
         </is>
       </c>
-      <c r="D148" s="3" t="n">
-        <v>0.488</v>
-      </c>
+      <c r="D148" s="3" t="inlineStr"/>
       <c r="E148" s="3" t="inlineStr">
         <is>
           <t>USD millions</t>
@@ -4749,7 +4737,7 @@
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -4973,9 +4961,6 @@
           <t>Prior Year</t>
         </is>
       </c>
-      <c r="D181" t="n">
-        <v>0.458</v>
-      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>USD millions</t>
@@ -5595,7 +5580,7 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>Actual</t>
+          <t xml:space="preserve"> actual </t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -5624,7 +5609,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1.169</v>
+        <v>23.38</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -5798,9 +5783,7 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="D214" s="3" t="n">
-        <v>3.877</v>
-      </c>
+      <c r="D214" s="3" t="inlineStr"/>
       <c r="E214" s="3" t="inlineStr">
         <is>
           <t>USD millions</t>
@@ -6499,7 +6482,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>0.482</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
@@ -6623,9 +6606,6 @@
           <t>Budget</t>
         </is>
       </c>
-      <c r="D247" t="n">
-        <v>3.754</v>
-      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>USD millions</t>
@@ -7320,7 +7300,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t xml:space="preserve"> budget </t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -8945,7 +8925,7 @@
       </c>
       <c r="C340" s="3" t="inlineStr">
         <is>
-          <t>Forecast</t>
+          <t xml:space="preserve"> forecast </t>
         </is>
       </c>
       <c r="D340" s="3" t="n">
@@ -10670,7 +10650,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Prior Year</t>
+          <t xml:space="preserve"> prior year </t>
         </is>
       </c>
       <c r="D409" t="n">
@@ -11645,7 +11625,7 @@
       </c>
       <c r="C448" s="3" t="inlineStr">
         <is>
-          <t>Forecast</t>
+          <t xml:space="preserve"> forecast </t>
         </is>
       </c>
       <c r="D448" s="3" t="n">
@@ -12482,8 +12462,308 @@
         </is>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" s="3" t="inlineStr">
+        <is>
+          <t>04/30/2025</t>
+        </is>
+      </c>
+      <c r="B482" s="3" t="inlineStr">
+        <is>
+          <t>Operating Expense</t>
+        </is>
+      </c>
+      <c r="C482" s="3" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="D482" s="3" t="n">
+        <v>3.881</v>
+      </c>
+      <c r="E482" s="3" t="inlineStr">
+        <is>
+          <t>USD millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>05/31/2025</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Operating Expense</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Prior Year</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>USD millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="3" t="inlineStr">
+        <is>
+          <t>06/30/2025</t>
+        </is>
+      </c>
+      <c r="B484" s="3" t="inlineStr">
+        <is>
+          <t>Loan Balance</t>
+        </is>
+      </c>
+      <c r="C484" s="3" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="D484" s="3" t="n">
+        <v>1700.946</v>
+      </c>
+      <c r="E484" s="3" t="inlineStr">
+        <is>
+          <t>USD millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>07/31/2025</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Deposit Balance</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>1521.924</v>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>USD millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="3" t="inlineStr">
+        <is>
+          <t>09/30/2025</t>
+        </is>
+      </c>
+      <c r="B486" s="3" t="inlineStr">
+        <is>
+          <t>Loan Interest</t>
+        </is>
+      </c>
+      <c r="C486" s="3" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="D486" s="3" t="n">
+        <v>5.726</v>
+      </c>
+      <c r="E486" s="3" t="inlineStr">
+        <is>
+          <t>USD millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>10/31/2025</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Loan Interest</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Prior Year</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>USD millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="3" t="inlineStr">
+        <is>
+          <t>11/30/2025</t>
+        </is>
+      </c>
+      <c r="B488" s="3" t="inlineStr">
+        <is>
+          <t>Treasury Fee</t>
+        </is>
+      </c>
+      <c r="C488" s="3" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="D488" s="3" t="n">
+        <v>2.348</v>
+      </c>
+      <c r="E488" s="3" t="inlineStr">
+        <is>
+          <t>USD millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>12/31/2025</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Deposit Fee</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>USD millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="3" t="inlineStr">
+        <is>
+          <t>01/31/2026</t>
+        </is>
+      </c>
+      <c r="B490" s="3" t="inlineStr">
+        <is>
+          <t>Merchant Fee</t>
+        </is>
+      </c>
+      <c r="C490" s="3" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="D490" s="3" t="n">
+        <v>1.202</v>
+      </c>
+      <c r="E490" s="3" t="inlineStr">
+        <is>
+          <t>USD millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>02/28/2026</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Merchant Fee</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Prior Year</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>USD millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="3" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="B492" s="3" t="inlineStr">
+        <is>
+          <t>FX Fee</t>
+        </is>
+      </c>
+      <c r="C492" s="3" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="D492" s="3" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="E492" s="3" t="inlineStr">
+        <is>
+          <t>USD millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>04/30/2026</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Operating Expense</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>USD millions</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E481"/>
+  <autoFilter ref="A1:E493"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>